--- a/Fiche de mouvement _06-2026.xlsx
+++ b/Fiche de mouvement _06-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr date1904="1" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\OneDrive\Documents\Samir\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB30C558-5B20-4AF5-9FC3-490149A67477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8815AF30-265F-4680-A487-B1474EB68051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DASHBOARD" sheetId="22" r:id="rId1"/>
@@ -2909,6 +2909,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2955,12 +2961,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -7817,7 +7817,7 @@
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="139" t="s">
         <v>397</v>
       </c>
       <c r="C9" s="41">
@@ -7837,7 +7837,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="139"/>
+      <c r="B10" s="141"/>
       <c r="C10" s="41">
         <v>46187</v>
       </c>
@@ -8552,7 +8552,7 @@
     </row>
     <row r="8" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19"/>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="139" t="s">
         <v>333</v>
       </c>
       <c r="C8" s="27">
@@ -8568,7 +8568,7 @@
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="83"/>
-      <c r="B9" s="139"/>
+      <c r="B9" s="141"/>
       <c r="C9" s="27">
         <v>15062026</v>
       </c>
@@ -10090,7 +10090,7 @@
       <c r="A12" s="38">
         <v>4</v>
       </c>
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="146" t="s">
         <v>427</v>
       </c>
       <c r="C12" s="28">
@@ -10110,7 +10110,7 @@
       <c r="A13" s="38">
         <v>5</v>
       </c>
-      <c r="B13" s="145"/>
+      <c r="B13" s="147"/>
       <c r="C13" s="28">
         <v>18062026</v>
       </c>
@@ -10148,7 +10148,7 @@
       <c r="A15" s="38">
         <v>7</v>
       </c>
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="138" t="s">
         <v>429</v>
       </c>
       <c r="C15" s="28">
@@ -10168,7 +10168,7 @@
       <c r="A16" s="38">
         <v>8</v>
       </c>
-      <c r="B16" s="136"/>
+      <c r="B16" s="138"/>
       <c r="C16" s="28">
         <v>18062026</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="A17" s="38">
         <v>9</v>
       </c>
-      <c r="B17" s="143" t="s">
+      <c r="B17" s="145" t="s">
         <v>430</v>
       </c>
       <c r="C17" s="28">
@@ -10206,7 +10206,7 @@
       <c r="A18" s="38">
         <v>10</v>
       </c>
-      <c r="B18" s="143"/>
+      <c r="B18" s="145"/>
       <c r="C18" s="28">
         <v>18062026</v>
       </c>
@@ -12723,7 +12723,7 @@
       <c r="A9" s="19">
         <v>1</v>
       </c>
-      <c r="B9" s="146" t="s">
+      <c r="B9" s="130" t="s">
         <v>473</v>
       </c>
       <c r="C9" s="27">
@@ -12743,7 +12743,7 @@
       <c r="A10" s="17">
         <v>2</v>
       </c>
-      <c r="B10" s="147"/>
+      <c r="B10" s="131"/>
       <c r="C10" s="28">
         <v>28062026</v>
       </c>
@@ -13786,7 +13786,7 @@
       <c r="A10" s="17">
         <v>2</v>
       </c>
-      <c r="B10" s="147" t="s">
+      <c r="B10" s="131" t="s">
         <v>518</v>
       </c>
       <c r="C10" s="126">
@@ -13806,7 +13806,7 @@
       <c r="A11" s="17">
         <v>3</v>
       </c>
-      <c r="B11" s="147"/>
+      <c r="B11" s="131"/>
       <c r="C11" s="126">
         <v>29062026</v>
       </c>
@@ -13824,7 +13824,7 @@
       <c r="A12" s="17">
         <v>4</v>
       </c>
-      <c r="B12" s="147"/>
+      <c r="B12" s="131"/>
       <c r="C12" s="126">
         <v>29062026</v>
       </c>
@@ -13908,7 +13908,7 @@
       <c r="A16" s="17">
         <v>8</v>
       </c>
-      <c r="B16" s="136" t="s">
+      <c r="B16" s="138" t="s">
         <v>516</v>
       </c>
       <c r="C16" s="126">
@@ -13928,7 +13928,7 @@
       <c r="A17" s="17">
         <v>9</v>
       </c>
-      <c r="B17" s="136"/>
+      <c r="B17" s="138"/>
       <c r="C17" s="126">
         <v>29062026</v>
       </c>
@@ -13946,7 +13946,7 @@
       <c r="A18" s="17">
         <v>10</v>
       </c>
-      <c r="B18" s="136"/>
+      <c r="B18" s="138"/>
       <c r="C18" s="126">
         <v>29062026</v>
       </c>
@@ -13964,7 +13964,7 @@
       <c r="A19" s="17">
         <v>11</v>
       </c>
-      <c r="B19" s="136"/>
+      <c r="B19" s="138"/>
       <c r="C19" s="126">
         <v>29062026</v>
       </c>
@@ -13983,7 +13983,7 @@
       <c r="A20" s="17">
         <v>12</v>
       </c>
-      <c r="B20" s="136"/>
+      <c r="B20" s="138"/>
       <c r="C20" s="126">
         <v>29062026</v>
       </c>
@@ -14002,7 +14002,7 @@
       <c r="A21" s="17">
         <v>13</v>
       </c>
-      <c r="B21" s="136"/>
+      <c r="B21" s="138"/>
       <c r="C21" s="126">
         <v>29062026</v>
       </c>
@@ -14021,7 +14021,7 @@
       <c r="A22" s="17">
         <v>14</v>
       </c>
-      <c r="B22" s="136"/>
+      <c r="B22" s="138"/>
       <c r="C22" s="126">
         <v>29062026</v>
       </c>
@@ -14509,7 +14509,7 @@
       <c r="A9" s="19">
         <v>1</v>
       </c>
-      <c r="B9" s="146"/>
+      <c r="B9" s="130"/>
       <c r="C9" s="27"/>
       <c r="D9" s="76"/>
       <c r="E9" s="111"/>
@@ -14519,7 +14519,7 @@
       <c r="A10" s="17">
         <v>2</v>
       </c>
-      <c r="B10" s="147"/>
+      <c r="B10" s="131"/>
       <c r="C10" s="28"/>
       <c r="D10" s="96"/>
       <c r="E10" s="108"/>
@@ -15105,7 +15105,7 @@
       <c r="A12" s="17">
         <v>4</v>
       </c>
-      <c r="B12" s="130"/>
+      <c r="B12" s="132"/>
       <c r="C12" s="28"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -15116,7 +15116,7 @@
       <c r="A13" s="17">
         <v>5</v>
       </c>
-      <c r="B13" s="130"/>
+      <c r="B13" s="132"/>
       <c r="C13" s="28"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
@@ -15668,7 +15668,7 @@
       <c r="A11" s="38">
         <v>3</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="133" t="s">
         <v>73</v>
       </c>
       <c r="C11" s="46">
@@ -15688,7 +15688,7 @@
       <c r="A12" s="38">
         <v>4</v>
       </c>
-      <c r="B12" s="132"/>
+      <c r="B12" s="134"/>
       <c r="C12" s="53"/>
       <c r="D12" s="47"/>
       <c r="E12" s="43"/>
@@ -15699,7 +15699,7 @@
       <c r="A13" s="38">
         <v>5</v>
       </c>
-      <c r="B13" s="132"/>
+      <c r="B13" s="134"/>
       <c r="C13" s="46">
         <v>46176</v>
       </c>
@@ -15717,7 +15717,7 @@
       <c r="A14" s="38">
         <v>6</v>
       </c>
-      <c r="B14" s="132"/>
+      <c r="B14" s="134"/>
       <c r="C14" s="46">
         <v>46176</v>
       </c>
@@ -15735,7 +15735,7 @@
       <c r="A15" s="38">
         <v>7</v>
       </c>
-      <c r="B15" s="132"/>
+      <c r="B15" s="134"/>
       <c r="C15" s="46">
         <v>46176</v>
       </c>
@@ -15753,7 +15753,7 @@
       <c r="A16" s="38">
         <v>8</v>
       </c>
-      <c r="B16" s="132"/>
+      <c r="B16" s="134"/>
       <c r="C16" s="46">
         <v>46176</v>
       </c>
@@ -15771,7 +15771,7 @@
       <c r="A17" s="38">
         <v>9</v>
       </c>
-      <c r="B17" s="132"/>
+      <c r="B17" s="134"/>
       <c r="C17" s="46">
         <v>46176</v>
       </c>
@@ -15790,7 +15790,7 @@
       <c r="A18" s="38">
         <v>10</v>
       </c>
-      <c r="B18" s="133"/>
+      <c r="B18" s="135"/>
       <c r="C18" s="46">
         <v>46176</v>
       </c>
@@ -15890,7 +15890,7 @@
       <c r="A23" s="38">
         <v>15</v>
       </c>
-      <c r="B23" s="131" t="s">
+      <c r="B23" s="133" t="s">
         <v>101</v>
       </c>
       <c r="C23" s="41">
@@ -15910,7 +15910,7 @@
       <c r="A24" s="38">
         <v>16</v>
       </c>
-      <c r="B24" s="132"/>
+      <c r="B24" s="134"/>
       <c r="C24" s="41">
         <v>46176</v>
       </c>
@@ -15928,7 +15928,7 @@
       <c r="A25" s="38">
         <v>17</v>
       </c>
-      <c r="B25" s="133"/>
+      <c r="B25" s="135"/>
       <c r="C25" s="41">
         <v>46176</v>
       </c>
@@ -15946,7 +15946,7 @@
       <c r="A26" s="38">
         <v>18</v>
       </c>
-      <c r="B26" s="131" t="s">
+      <c r="B26" s="133" t="s">
         <v>108</v>
       </c>
       <c r="C26" s="41">
@@ -15966,7 +15966,7 @@
       <c r="A27" s="38">
         <v>19</v>
       </c>
-      <c r="B27" s="132"/>
+      <c r="B27" s="134"/>
       <c r="C27" s="41">
         <v>46176</v>
       </c>
@@ -15984,7 +15984,7 @@
       <c r="A28" s="38">
         <v>20</v>
       </c>
-      <c r="B28" s="133"/>
+      <c r="B28" s="135"/>
       <c r="C28" s="41">
         <v>46176</v>
       </c>
@@ -16002,7 +16002,7 @@
       <c r="A29" s="38">
         <v>21</v>
       </c>
-      <c r="B29" s="131" t="s">
+      <c r="B29" s="133" t="s">
         <v>115</v>
       </c>
       <c r="C29" s="41">
@@ -16022,7 +16022,7 @@
       <c r="A30" s="38">
         <v>22</v>
       </c>
-      <c r="B30" s="132"/>
+      <c r="B30" s="134"/>
       <c r="C30" s="41">
         <v>46176</v>
       </c>
@@ -16040,7 +16040,7 @@
       <c r="A31" s="38">
         <v>23</v>
       </c>
-      <c r="B31" s="132"/>
+      <c r="B31" s="134"/>
       <c r="C31" s="53"/>
       <c r="D31" s="47"/>
       <c r="E31" s="42"/>
@@ -16050,7 +16050,7 @@
       <c r="A32" s="38">
         <v>24</v>
       </c>
-      <c r="B32" s="133"/>
+      <c r="B32" s="135"/>
       <c r="C32" s="41">
         <v>46176</v>
       </c>
@@ -16170,7 +16170,7 @@
       <c r="A39" s="38">
         <v>31</v>
       </c>
-      <c r="B39" s="131" t="s">
+      <c r="B39" s="133" t="s">
         <v>142</v>
       </c>
       <c r="C39" s="41">
@@ -16190,7 +16190,7 @@
       <c r="A40" s="38">
         <v>32</v>
       </c>
-      <c r="B40" s="132"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="53"/>
       <c r="D40" s="47"/>
       <c r="E40" s="42"/>
@@ -16200,7 +16200,7 @@
       <c r="A41" s="38">
         <v>33</v>
       </c>
-      <c r="B41" s="132"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="53"/>
       <c r="D41" s="47"/>
       <c r="E41" s="42"/>
@@ -16210,7 +16210,7 @@
       <c r="A42" s="38">
         <v>34</v>
       </c>
-      <c r="B42" s="133"/>
+      <c r="B42" s="135"/>
       <c r="C42" s="53"/>
       <c r="D42" s="47"/>
       <c r="E42" s="42"/>
@@ -16221,7 +16221,7 @@
       <c r="A43" s="38">
         <v>35</v>
       </c>
-      <c r="B43" s="131" t="s">
+      <c r="B43" s="133" t="s">
         <v>148</v>
       </c>
       <c r="C43" s="41">
@@ -16242,7 +16242,7 @@
       <c r="A44" s="38">
         <v>36</v>
       </c>
-      <c r="B44" s="133"/>
+      <c r="B44" s="135"/>
       <c r="C44" s="41">
         <v>46176</v>
       </c>
@@ -16261,7 +16261,7 @@
       <c r="A45" s="38">
         <v>37</v>
       </c>
-      <c r="B45" s="134" t="s">
+      <c r="B45" s="136" t="s">
         <v>48</v>
       </c>
       <c r="C45" s="41">
@@ -16281,7 +16281,7 @@
       <c r="A46" s="38">
         <v>38</v>
       </c>
-      <c r="B46" s="135"/>
+      <c r="B46" s="137"/>
       <c r="C46" s="41">
         <v>46176</v>
       </c>
@@ -16719,7 +16719,7 @@
       <c r="A13" s="17">
         <v>5</v>
       </c>
-      <c r="B13" s="136"/>
+      <c r="B13" s="138"/>
       <c r="C13" s="63"/>
       <c r="D13" s="42"/>
       <c r="E13" s="42"/>
@@ -16729,7 +16729,7 @@
       <c r="A14" s="17">
         <v>6</v>
       </c>
-      <c r="B14" s="136"/>
+      <c r="B14" s="138"/>
       <c r="C14" s="63"/>
       <c r="D14" s="42"/>
       <c r="E14" s="42"/>
@@ -16739,7 +16739,7 @@
       <c r="A15" s="17">
         <v>7</v>
       </c>
-      <c r="B15" s="136"/>
+      <c r="B15" s="138"/>
       <c r="C15" s="63"/>
       <c r="D15" s="42"/>
       <c r="E15" s="42"/>
@@ -17168,7 +17168,7 @@
       <c r="A9" s="38">
         <v>1</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="139" t="s">
         <v>180</v>
       </c>
       <c r="C9" s="41">
@@ -17188,7 +17188,7 @@
       <c r="A10" s="38">
         <v>2</v>
       </c>
-      <c r="B10" s="138"/>
+      <c r="B10" s="140"/>
       <c r="C10" s="41">
         <v>46180</v>
       </c>
@@ -17206,7 +17206,7 @@
       <c r="A11" s="38">
         <v>3</v>
       </c>
-      <c r="B11" s="138"/>
+      <c r="B11" s="140"/>
       <c r="C11" s="41">
         <v>46180</v>
       </c>
@@ -17224,7 +17224,7 @@
       <c r="A12" s="38">
         <v>4</v>
       </c>
-      <c r="B12" s="138"/>
+      <c r="B12" s="140"/>
       <c r="C12" s="41">
         <v>46180</v>
       </c>
@@ -17243,7 +17243,7 @@
       <c r="A13" s="38">
         <v>5</v>
       </c>
-      <c r="B13" s="138"/>
+      <c r="B13" s="140"/>
       <c r="C13" s="41">
         <v>46180</v>
       </c>
@@ -17261,7 +17261,7 @@
       <c r="A14" s="38">
         <v>6</v>
       </c>
-      <c r="B14" s="138"/>
+      <c r="B14" s="140"/>
       <c r="C14" s="41">
         <v>46180</v>
       </c>
@@ -17279,7 +17279,7 @@
       <c r="A15" s="38">
         <v>7</v>
       </c>
-      <c r="B15" s="139"/>
+      <c r="B15" s="141"/>
       <c r="C15" s="41">
         <v>46180</v>
       </c>
@@ -17297,7 +17297,7 @@
       <c r="A16" s="38">
         <v>8</v>
       </c>
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="139" t="s">
         <v>181</v>
       </c>
       <c r="C16" s="41">
@@ -17317,7 +17317,7 @@
       <c r="A17" s="38">
         <v>9</v>
       </c>
-      <c r="B17" s="139"/>
+      <c r="B17" s="141"/>
       <c r="C17" s="41">
         <v>46180</v>
       </c>
@@ -17774,7 +17774,7 @@
       <c r="A8" s="38">
         <v>1</v>
       </c>
-      <c r="B8" s="136" t="s">
+      <c r="B8" s="138" t="s">
         <v>142</v>
       </c>
       <c r="C8" s="41">
@@ -17794,7 +17794,7 @@
       <c r="A9" s="38">
         <v>2</v>
       </c>
-      <c r="B9" s="136"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="41">
         <v>46181</v>
       </c>
@@ -17812,7 +17812,7 @@
       <c r="A10" s="38">
         <v>3</v>
       </c>
-      <c r="B10" s="136"/>
+      <c r="B10" s="138"/>
       <c r="C10" s="41"/>
       <c r="D10" s="42"/>
       <c r="E10" s="42"/>
@@ -18591,7 +18591,7 @@
       <c r="A9" s="38">
         <v>2</v>
       </c>
-      <c r="B9" s="136" t="s">
+      <c r="B9" s="138" t="s">
         <v>260</v>
       </c>
       <c r="C9" s="41">
@@ -18611,7 +18611,7 @@
       <c r="A10" s="38">
         <v>3</v>
       </c>
-      <c r="B10" s="136"/>
+      <c r="B10" s="138"/>
       <c r="C10" s="41">
         <v>46182</v>
       </c>
@@ -18629,7 +18629,7 @@
       <c r="A11" s="38">
         <v>4</v>
       </c>
-      <c r="B11" s="136"/>
+      <c r="B11" s="138"/>
       <c r="C11" s="41">
         <v>46182</v>
       </c>
@@ -18647,7 +18647,7 @@
       <c r="A12" s="38">
         <v>5</v>
       </c>
-      <c r="B12" s="136"/>
+      <c r="B12" s="138"/>
       <c r="C12" s="41">
         <v>46182</v>
       </c>
@@ -18665,7 +18665,7 @@
       <c r="A13" s="38">
         <v>6</v>
       </c>
-      <c r="B13" s="136"/>
+      <c r="B13" s="138"/>
       <c r="C13" s="41">
         <v>46182</v>
       </c>
@@ -18683,7 +18683,7 @@
       <c r="A14" s="38">
         <v>7</v>
       </c>
-      <c r="B14" s="136"/>
+      <c r="B14" s="138"/>
       <c r="C14" s="41"/>
       <c r="D14" s="74"/>
       <c r="E14" s="74"/>
@@ -18693,7 +18693,7 @@
       <c r="A15" s="38">
         <v>8</v>
       </c>
-      <c r="B15" s="136"/>
+      <c r="B15" s="138"/>
       <c r="C15" s="41">
         <v>46182</v>
       </c>
@@ -18711,7 +18711,7 @@
       <c r="A16" s="38">
         <v>9</v>
       </c>
-      <c r="B16" s="136"/>
+      <c r="B16" s="138"/>
       <c r="C16" s="41">
         <v>46182</v>
       </c>
@@ -18730,7 +18730,7 @@
       <c r="A17" s="38">
         <v>10</v>
       </c>
-      <c r="B17" s="136"/>
+      <c r="B17" s="138"/>
       <c r="C17" s="41">
         <v>46182</v>
       </c>
@@ -18749,7 +18749,7 @@
       <c r="A18" s="38">
         <v>11</v>
       </c>
-      <c r="B18" s="136"/>
+      <c r="B18" s="138"/>
       <c r="C18" s="41">
         <v>46182</v>
       </c>
@@ -18768,7 +18768,7 @@
       <c r="A19" s="38">
         <v>12</v>
       </c>
-      <c r="B19" s="136"/>
+      <c r="B19" s="138"/>
       <c r="C19" s="41">
         <v>46182</v>
       </c>
@@ -18786,7 +18786,7 @@
       <c r="A20" s="38">
         <v>13</v>
       </c>
-      <c r="B20" s="136"/>
+      <c r="B20" s="138"/>
       <c r="C20" s="41"/>
       <c r="D20" s="74"/>
       <c r="E20" s="74"/>
@@ -18796,7 +18796,7 @@
       <c r="A21" s="38">
         <v>14</v>
       </c>
-      <c r="B21" s="136"/>
+      <c r="B21" s="138"/>
       <c r="C21" s="41">
         <v>46182</v>
       </c>
@@ -18814,7 +18814,7 @@
       <c r="A22" s="38">
         <v>15</v>
       </c>
-      <c r="B22" s="136"/>
+      <c r="B22" s="138"/>
       <c r="C22" s="41">
         <v>46182</v>
       </c>
@@ -18832,7 +18832,7 @@
       <c r="A23" s="38">
         <v>16</v>
       </c>
-      <c r="B23" s="136"/>
+      <c r="B23" s="138"/>
       <c r="C23" s="41">
         <v>46182</v>
       </c>
@@ -18850,7 +18850,7 @@
       <c r="A24" s="38">
         <v>17</v>
       </c>
-      <c r="B24" s="136"/>
+      <c r="B24" s="138"/>
       <c r="C24" s="41">
         <v>46182</v>
       </c>
@@ -18868,7 +18868,7 @@
       <c r="A25" s="38">
         <v>18</v>
       </c>
-      <c r="B25" s="136"/>
+      <c r="B25" s="138"/>
       <c r="C25" s="41">
         <v>46182</v>
       </c>
@@ -18886,7 +18886,7 @@
       <c r="A26" s="38">
         <v>19</v>
       </c>
-      <c r="B26" s="136"/>
+      <c r="B26" s="138"/>
       <c r="C26" s="41">
         <v>46182</v>
       </c>
@@ -18904,7 +18904,7 @@
       <c r="A27" s="38">
         <v>20</v>
       </c>
-      <c r="B27" s="136"/>
+      <c r="B27" s="138"/>
       <c r="C27" s="41">
         <v>46182</v>
       </c>
@@ -18922,7 +18922,7 @@
       <c r="A28" s="38">
         <v>21</v>
       </c>
-      <c r="B28" s="136"/>
+      <c r="B28" s="138"/>
       <c r="C28" s="41">
         <v>46182</v>
       </c>
@@ -18940,7 +18940,7 @@
       <c r="A29" s="38">
         <v>22</v>
       </c>
-      <c r="B29" s="136"/>
+      <c r="B29" s="138"/>
       <c r="C29" s="41">
         <v>46182</v>
       </c>
@@ -18958,7 +18958,7 @@
       <c r="A30" s="38">
         <v>23</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="138"/>
       <c r="C30" s="41">
         <v>46182</v>
       </c>
@@ -18976,7 +18976,7 @@
       <c r="A31" s="38">
         <v>24</v>
       </c>
-      <c r="B31" s="140" t="s">
+      <c r="B31" s="142" t="s">
         <v>261</v>
       </c>
       <c r="C31" s="41">
@@ -18996,7 +18996,7 @@
       <c r="A32" s="38">
         <v>25</v>
       </c>
-      <c r="B32" s="141"/>
+      <c r="B32" s="143"/>
       <c r="C32" s="41">
         <v>46182</v>
       </c>
@@ -19014,7 +19014,7 @@
       <c r="A33" s="38">
         <v>26</v>
       </c>
-      <c r="B33" s="141"/>
+      <c r="B33" s="143"/>
       <c r="C33" s="41">
         <v>46182</v>
       </c>
@@ -19032,7 +19032,7 @@
       <c r="A34" s="38">
         <v>27</v>
       </c>
-      <c r="B34" s="141"/>
+      <c r="B34" s="143"/>
       <c r="C34" s="41">
         <v>46182</v>
       </c>
@@ -19050,7 +19050,7 @@
       <c r="A35" s="38">
         <v>28</v>
       </c>
-      <c r="B35" s="141"/>
+      <c r="B35" s="143"/>
       <c r="C35" s="41">
         <v>46182</v>
       </c>
@@ -19068,7 +19068,7 @@
       <c r="A36" s="38">
         <v>29</v>
       </c>
-      <c r="B36" s="141"/>
+      <c r="B36" s="143"/>
       <c r="C36" s="41">
         <v>46182</v>
       </c>
@@ -19086,7 +19086,7 @@
       <c r="A37" s="38">
         <v>30</v>
       </c>
-      <c r="B37" s="141"/>
+      <c r="B37" s="143"/>
       <c r="C37" s="41">
         <v>46182</v>
       </c>
@@ -19104,7 +19104,7 @@
       <c r="A38" s="38">
         <v>31</v>
       </c>
-      <c r="B38" s="141"/>
+      <c r="B38" s="143"/>
       <c r="C38" s="41"/>
       <c r="D38" s="74"/>
       <c r="E38" s="74"/>
@@ -19114,7 +19114,7 @@
       <c r="A39" s="38">
         <v>32</v>
       </c>
-      <c r="B39" s="141"/>
+      <c r="B39" s="143"/>
       <c r="C39" s="41">
         <v>46182</v>
       </c>
@@ -19132,7 +19132,7 @@
       <c r="A40" s="38">
         <v>33</v>
       </c>
-      <c r="B40" s="141"/>
+      <c r="B40" s="143"/>
       <c r="C40" s="41">
         <v>46182</v>
       </c>
@@ -19150,7 +19150,7 @@
       <c r="A41" s="38">
         <v>34</v>
       </c>
-      <c r="B41" s="141"/>
+      <c r="B41" s="143"/>
       <c r="C41" s="41">
         <v>46182</v>
       </c>
@@ -19169,7 +19169,7 @@
       <c r="A42" s="38">
         <v>35</v>
       </c>
-      <c r="B42" s="141"/>
+      <c r="B42" s="143"/>
       <c r="C42" s="41">
         <v>46182</v>
       </c>
@@ -19188,7 +19188,7 @@
       <c r="A43" s="38">
         <v>36</v>
       </c>
-      <c r="B43" s="141"/>
+      <c r="B43" s="143"/>
       <c r="C43" s="41">
         <v>46182</v>
       </c>
@@ -19207,7 +19207,7 @@
       <c r="A44" s="38">
         <v>37</v>
       </c>
-      <c r="B44" s="141"/>
+      <c r="B44" s="143"/>
       <c r="C44" s="41"/>
       <c r="D44" s="74"/>
       <c r="E44" s="74"/>
@@ -19217,7 +19217,7 @@
       <c r="A45" s="38">
         <v>38</v>
       </c>
-      <c r="B45" s="141"/>
+      <c r="B45" s="143"/>
       <c r="C45" s="41">
         <v>46182</v>
       </c>
@@ -19235,7 +19235,7 @@
       <c r="A46" s="38">
         <v>39</v>
       </c>
-      <c r="B46" s="142"/>
+      <c r="B46" s="144"/>
       <c r="C46" s="41">
         <v>46182</v>
       </c>
@@ -19818,14 +19818,14 @@
         <v>583</v>
       </c>
       <c r="G8" s="127">
-        <v>46197</v>
+        <v>44736</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="139" t="s">
         <v>260</v>
       </c>
       <c r="C9" s="41">
@@ -19845,7 +19845,7 @@
       <c r="A10" s="17">
         <v>3</v>
       </c>
-      <c r="B10" s="139"/>
+      <c r="B10" s="141"/>
       <c r="C10" s="41">
         <v>46183</v>
       </c>
@@ -19863,7 +19863,7 @@
       <c r="A11" s="17">
         <v>4</v>
       </c>
-      <c r="B11" s="136" t="s">
+      <c r="B11" s="138" t="s">
         <v>261</v>
       </c>
       <c r="C11" s="41">
@@ -19884,7 +19884,7 @@
       <c r="A12" s="17">
         <v>5</v>
       </c>
-      <c r="B12" s="136"/>
+      <c r="B12" s="138"/>
       <c r="C12" s="41">
         <v>46183</v>
       </c>
